--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487893_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487893_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9564</v>
+        <v>1.5571</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6037</v>
+        <v>1.175</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3527</v>
+        <v>0.3821</v>
       </c>
       <c r="G2" t="n">
         <v>0.2906</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0196</v>
+        <v>-0.3797</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0033</v>
+        <v>-0.4319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0229</v>
+        <v>0.0522</v>
       </c>
       <c r="V2" t="n">
         <v>0.8137</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5169</v>
+        <v>0.2011</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1318</v>
+        <v>-0.0069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.208</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.674</v>
+        <v>0.1032</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5925</v>
+        <v>-0.0788</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.2665</v>
+        <v>0.1821</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0584</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2296</v>
+        <v>0.0192</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3112</v>
+        <v>0.0392</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5924</v>
+        <v>0.0449</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6371</v>
+        <v>-0.098</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9553</v>
+        <v>0.1429</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>0.2081</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0046</v>
+        <v>-0.1103</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2396</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2442</v>
+        <v>-0.045</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5213</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1424</v>
+        <v>0.0434</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0069</v>
+        <v>0.0406</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1492</v>
+        <v>0.0028</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1032</v>
+        <v>-2.674</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0788</v>
+        <v>0.5925</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1821</v>
+        <v>-3.2665</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0584</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0192</v>
+        <v>1.2296</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0392</v>
+        <v>-1.3112</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0449</v>
+        <v>-2.5924</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.098</v>
+        <v>-0.6371</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1429</v>
+        <v>-1.9553</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.169</v>
+        <v>-0.4689</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-1.0672</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1037</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.5213</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1531</v>
+        <v>-1.1238</v>
       </c>
       <c r="E5" t="n">
         <v>-0.9562</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.197</v>
+        <v>-0.1676</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8993</v>
@@ -844,13 +844,13 @@
         <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4619</v>
+        <v>-0.4325</v>
       </c>
       <c r="T5" t="n">
         <v>-0.261</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2009</v>
+        <v>-0.1716</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6406</v>
+        <v>-1.3866</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2155</v>
+        <v>-1.1083</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4251</v>
+        <v>-0.2783</v>
       </c>
       <c r="G6" t="n">
         <v>-0.592</v>
@@ -922,13 +922,13 @@
         <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2161</v>
+        <v>-0.9621</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5219</v>
+        <v>-0.4148</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5473</v>
       </c>
       <c r="V6" t="n">
         <v>0.5838</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2514</v>
+        <v>-1.6805</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3336</v>
+        <v>1.4641</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.585</v>
+        <v>-3.1446</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6201</v>
@@ -1000,13 +1000,13 @@
         <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3217</v>
+        <v>0.2492</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.721</v>
+        <v>-0.5905</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3993</v>
+        <v>0.8397</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9340000000000001</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8183</v>
+        <v>-2.535</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0453</v>
+        <v>0.0619</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7731</v>
+        <v>-2.5969</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6096</v>
@@ -1078,13 +1078,13 @@
         <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2494</v>
+        <v>-0.9661</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>-0.6105</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5317</v>
+        <v>-0.3555</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1675</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2552</v>
+        <v>-3.8543</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0114</v>
+        <v>-0.861</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2438</v>
+        <v>-2.9934</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.4633</v>
+        <v>-1.7752</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.0109</v>
+        <v>1.3688</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4524</v>
+        <v>-3.144</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8219</v>
+        <v>2.2663</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.9003</v>
+        <v>2.5284</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0784</v>
+        <v>-0.2621</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6414</v>
+        <v>-4.0415</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1106</v>
+        <v>-1.1596</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5308</v>
+        <v>-2.882</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.3705</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2081</v>
+        <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0588</v>
+        <v>0.1848</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5806</v>
+        <v>-0.5081</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4783</v>
+        <v>0.6929</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9411</v>
+        <v>0.2335</v>
       </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>1.7513</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7111</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1876</v>
+        <v>-3.9313</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8849</v>
+        <v>-2.4819</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3027</v>
+        <v>-1.4494</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5742</v>
+        <v>-5.4633</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.137</v>
+        <v>-4.0109</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4371</v>
+        <v>-1.4524</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5452</v>
+        <v>-2.8219</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6022999999999999</v>
+        <v>-2.9003</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0572</v>
+        <v>0.0784</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.1193</v>
+        <v>-2.6414</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7394</v>
+        <v>-1.1106</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.38</v>
+        <v>-1.5308</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0812</v>
+        <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2342</v>
+        <v>0.3828</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8515</v>
+        <v>0.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0857</v>
+        <v>0.2727</v>
       </c>
       <c r="V10" t="n">
-        <v>1.401</v>
+        <v>0.9411</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7513</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3503</v>
+        <v>0.7111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6447</v>
+        <v>-4.0087</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8601</v>
+        <v>-1.6472</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7846</v>
+        <v>-2.3615</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8621</v>
+        <v>-4.5742</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1278</v>
+        <v>-1.137</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.7343</v>
+        <v>-3.4371</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1267</v>
+        <v>0.5452</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2236</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3504</v>
+        <v>-0.0572</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.7354</v>
+        <v>-5.1193</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3515</v>
+        <v>-1.7394</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3839</v>
+        <v>-3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2081</v>
+        <v>-3.3299</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5271</v>
+        <v>0.4131</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5252</v>
+        <v>-0.6138</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0524</v>
+        <v>1.027</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5178</v>
+        <v>1.401</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5178</v>
+        <v>-0.3503</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8729</v>
+        <v>-4.8371</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5272</v>
+        <v>-0.7296</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3457</v>
+        <v>-4.1075</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7752</v>
+        <v>-3.8621</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3688</v>
+        <v>-0.1278</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.144</v>
+        <v>-3.7343</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2663</v>
+        <v>-0.1267</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5284</v>
+        <v>1.2236</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2621</v>
+        <v>-1.3504</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0415</v>
+        <v>-3.7354</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1596</v>
+        <v>-1.3515</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.882</v>
+        <v>-2.3839</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4974</v>
+        <v>0.2081</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.3705</v>
+        <v>-0.2081</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8338</v>
+        <v>0.3347</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1744</v>
+        <v>-0.3948</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3406</v>
+        <v>0.7294</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2335</v>
+        <v>-1.5178</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>-1.5178</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-22.2081</v>
+        <v>-21.5557</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.702</v>
+        <v>-5.0495</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.5064</v>
+        <v>-16.5063</v>
       </c>
       <c r="G13" t="n">
         <v>-21.676</v>
@@ -1444,7 +1444,7 @@
         <v>4.717300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>6.350099999999999</v>
+        <v>6.3501</v>
       </c>
       <c r="L13" t="n">
         <v>-1.6329</v>
@@ -1459,7 +1459,7 @@
         <v>-17.4305</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-3.885780586188048e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.4465</v>
@@ -1468,22 +1468,22 @@
         <v>11.4466</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4076</v>
+        <v>-1.755</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.500200000000001</v>
+        <v>-4.8478</v>
       </c>
       <c r="U13" t="n">
-        <v>3.093</v>
+        <v>3.0928</v>
       </c>
       <c r="V13" t="n">
         <v>1.8751</v>
       </c>
       <c r="W13" t="n">
-        <v>6.5276</v>
+        <v>6.527600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.652500000000001</v>
+        <v>-4.6525</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.4786</v>
+        <v>9.5215</v>
       </c>
       <c r="E14" t="n">
-        <v>6.505</v>
+        <v>6.0764</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9736</v>
+        <v>3.4452</v>
       </c>
       <c r="G14" t="n">
         <v>8.0343</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0708</v>
+        <v>1.1137</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3972</v>
+        <v>-0.0314</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6735</v>
+        <v>1.1451</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2914</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1003</v>
+        <v>6.8328</v>
       </c>
       <c r="E15" t="n">
-        <v>6.9747</v>
+        <v>7.2962</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8744</v>
+        <v>-0.4633</v>
       </c>
       <c r="G15" t="n">
         <v>6.9726</v>
@@ -1624,13 +1624,13 @@
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2885</v>
+        <v>-0.556</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0967</v>
+        <v>-0.7753</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1918</v>
+        <v>0.2193</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6162</v>
+        <v>5.2947</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0866</v>
+        <v>3.7651</v>
       </c>
       <c r="F16" t="n">
         <v>1.5296</v>
@@ -1702,10 +1702,10 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7672</v>
+        <v>0.4458</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1924</v>
+        <v>-0.129</v>
       </c>
       <c r="U16" t="n">
         <v>0.5748</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.876</v>
+        <v>4.5967</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5062</v>
+        <v>1.2563</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3698</v>
+        <v>3.3404</v>
       </c>
       <c r="G17" t="n">
         <v>6.2873</v>
@@ -1780,13 +1780,13 @@
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3301</v>
+        <v>0.3906</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2925</v>
+        <v>-0.5424</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9624</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4479</v>
+        <v>3.2377</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1278</v>
+        <v>1.7708</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3201</v>
+        <v>1.4669</v>
       </c>
       <c r="G18" t="n">
         <v>3.1731</v>
@@ -1858,13 +1858,13 @@
         <v>1.4568</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3308</v>
+        <v>0.459</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2272</v>
+        <v>-0.5843</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8965</v>
+        <v>1.0433</v>
       </c>
       <c r="V18" t="n">
         <v>0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7287</v>
+        <v>0.739</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4519</v>
+        <v>1.3448</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7232</v>
+        <v>-0.6058</v>
       </c>
       <c r="G19" t="n">
         <v>0.759</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5317</v>
+        <v>0.542</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1214</v>
+        <v>-0.2286</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6531</v>
+        <v>0.7705</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3538</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-1.1218</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.281</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.286</v>
+        <v>-0.1979</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1356</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0712</v>
+        <v>0.5164</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5153</v>
+        <v>-0.1276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.644</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.123</v>
+        <v>-3.1142</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0019</v>
+        <v>-1.7876</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.121</v>
+        <v>-1.3266</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5294</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5904</v>
+        <v>-0.5816</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1273</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0437</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3498</v>
+        <v>-3.7784</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8631</v>
+        <v>-2.2917</v>
       </c>
       <c r="F22" t="n">
         <v>-1.4866</v>
@@ -2170,10 +2170,10 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5063</v>
+        <v>0.0776</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2577</v>
+        <v>-0.171</v>
       </c>
       <c r="U22" t="n">
         <v>0.2486</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>22.2079</v>
+        <v>22.208</v>
       </c>
       <c r="E23" t="n">
-        <v>16.5062</v>
+        <v>16.5064</v>
       </c>
       <c r="F23" t="n">
-        <v>5.701899999999999</v>
+        <v>5.7019</v>
       </c>
       <c r="G23" t="n">
         <v>21.676</v>
@@ -2248,10 +2248,10 @@
         <v>11.4464</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4074</v>
+        <v>2.4075</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0929</v>
+        <v>-3.093</v>
       </c>
       <c r="U23" t="n">
         <v>5.500299999999999</v>
